--- a/backend/data/attachments/railway/Takraf_EDK500.xlsx
+++ b/backend/data/attachments/railway/Takraf_EDK500.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\crane_lifting_capacity\data\railway\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\crane_lifting_capacity\cranes\railway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB00B90C-6AC9-4487-AFF7-BA7A1A9BAE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5F7A71-4188-4743-9335-A0205E552616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{D0CD5142-251E-41F7-B82A-77810B023ACC}"/>
   </bookViews>
@@ -501,9 +501,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -511,9 +508,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -552,9 +546,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -585,9 +576,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,6 +583,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -931,7 +931,7 @@
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
     </row>
@@ -942,7 +942,7 @@
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="16">
         <v>5870.25</v>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>5</v>
       </c>
     </row>
@@ -964,7 +964,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="16">
         <v>996.74</v>
       </c>
     </row>
@@ -975,61 +975,61 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="28">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="35"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="12"/>
+      <c r="C7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="35"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="32">
-        <v>6.25</v>
-      </c>
-      <c r="C9" s="16">
+        <v>6.3</v>
+      </c>
+      <c r="C9" s="14">
         <v>80</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="15">
         <v>50</v>
       </c>
       <c r="E9" s="2">
@@ -1043,402 +1043,402 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+      <c r="B10" s="33">
         <v>7</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>67.7</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="10">
         <v>41.5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>17.2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>38.799999999999997</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
+      <c r="B11" s="34">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>56.2</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <v>33.700000000000003</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <v>13.6</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="8">
         <v>34.9</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <v>24.6</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+      <c r="B12" s="33">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>48</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="10">
         <v>29.2</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>10.7</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>31.4</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
+      <c r="B13" s="34">
         <v>10</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>41.2</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11">
         <v>25.1</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <v>8.6</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="8">
         <v>28.7</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <v>19.399999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
+      <c r="B14" s="33">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>36.200000000000003</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>21.8</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>7.3</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>25.8</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>17.100000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="8">
+      <c r="B15" s="34">
         <v>12</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>31.9</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>19.100000000000001</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>6.5</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="8">
         <v>23.1</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <v>14.9</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
+      <c r="B16" s="33">
         <v>13</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>28.7</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>16.7</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <v>5.7</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>20.6</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="B17" s="34">
         <v>14</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>25.4</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="11">
         <v>14.8</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="8">
         <v>5</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="8">
         <v>18.600000000000001</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="9">
         <v>11.4</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="4">
+      <c r="B18" s="33">
         <v>15</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>22.6</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>13.4</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>4.5</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>16.5</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="8">
+      <c r="B19" s="34">
         <v>16</v>
       </c>
-      <c r="C19" s="9">
-        <v>20</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="C19" s="7">
+        <v>20</v>
+      </c>
+      <c r="D19" s="11">
         <v>12</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <v>3.9</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="8">
         <v>14.6</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="9">
         <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
+      <c r="B20" s="33">
         <v>17</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>18</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="10">
         <v>10.9</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>3.4</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>12.8</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="8">
+      <c r="B21" s="34">
         <v>18</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>16.5</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="11">
         <v>10</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <v>3</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="8">
         <v>11.7</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="9">
         <v>6.2</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4">
+      <c r="B22" s="33">
         <v>19</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>15.2</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="10">
         <v>9.1</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>2.6</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
         <v>10.199999999999999</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="6">
         <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="8">
-        <v>20</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="34">
+        <v>20</v>
+      </c>
+      <c r="C23" s="7">
         <v>14.1</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="11">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="8">
         <v>8.9</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="9">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="4">
+      <c r="B24" s="33">
         <v>21</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>13</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="10">
         <v>7.3</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>1.8</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>7.7</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="6">
         <v>3.3</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="8">
+      <c r="B25" s="34">
         <v>22</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="C25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="8">
         <v>6.6</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="9">
         <v>2.7</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="4">
+      <c r="B26" s="33">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="C26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="5">
         <v>4.8</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="6">
         <v>1.7</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="8">
+      <c r="B27" s="34">
         <v>26</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="C27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="8">
         <v>3.6</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="9">
         <v>1.2</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="21">
+      <c r="B28" s="35">
         <v>28</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="24">
+      <c r="C28" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="21">
         <v>2.7</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="22">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="30">
+      <c r="B29" s="27">
         <v>28.7</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="28">
+      <c r="C29" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="25">
         <v>2.5</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="26">
         <v>1</v>
       </c>
     </row>
